--- a/Final_Task/DQ_final_task_Aliaksei_Papou.xlsx
+++ b/Final_Task/DQ_final_task_Aliaksei_Papou.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -52,6 +52,9 @@
     <t xml:space="preserve">Ensure that data can be cast to target types: Rating (Decimal), Reviews (Integer), Last Updated (Date).</t>
   </si>
   <si>
+    <t xml:space="preserve">SELECT "Rating", "Reviews", "Last Updated" FROM google_play_store WHERE "Rating"::text !~ '^[0-9]+(\.[0-9]+)?$' OR "Reviews"::text !~ '^[0-9]+$' OR "Last Updated"::text !~ '^\d{4}-\d{2}-\d{2}$'; </t>
+  </si>
+  <si>
     <t xml:space="preserve">Uniqueness</t>
   </si>
   <si>
@@ -73,7 +76,7 @@
     <t xml:space="preserve">Mandatory columns (Not Null = Y) must not contain NULL values.</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT * FROM google_play_store WHERE "App" IS NULL OR "Category" IS NULL OR "Price" IS NULL OR "Genres" IS NULL;</t>
+    <t xml:space="preserve">SELECT * FROM google_play_store  WHERE "App" IS NULL OR "Category" IS NULL OR "Price" IS NULL  OR "Genres" IS NULL OR "Last Updated" IS NULL;</t>
   </si>
   <si>
     <t xml:space="preserve">Validity</t>
@@ -94,7 +97,7 @@
     <t xml:space="preserve">Ensure date follows a valid date format.</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT "Last Updated" FROM google_play_store WHERE "Last Updated" IS NOT NULL AND is_date("Last Updated") = FALSE;</t>
+    <t xml:space="preserve">SELECT "Last Updated"  FROM google_play_store  WHERE "Last Updated" IS NOT NULL  AND "Last Updated"::text !~ '^\d{4}-\d{2}-\d{2}$'; </t>
   </si>
   <si>
     <t xml:space="preserve">App, Category, Size, Installs, Type, Price, Content Rating, Genres, Current Ver, Android Ver</t>
@@ -148,6 +151,9 @@
     <t xml:space="preserve">Ensure that values can be cast to Decimal(11,10).</t>
   </si>
   <si>
+    <t xml:space="preserve">SELECT "Sentiment_Polarity", "Sentiment_Subjectivity"  FROM google_play_store_user_reviews  WHERE "Sentiment_Polarity"::text !~ '^-?\d{1}(\.\d+)?$' OR "Sentiment_Subjectivity"::text !~ '^-?\d{1}(\.\d+)?$';</t>
+  </si>
+  <si>
     <t xml:space="preserve">App, Translated_Review</t>
   </si>
   <si>
@@ -190,7 +196,7 @@
     <t xml:space="preserve">Must be 'Positive', 'Negative', or 'Neutral'. If Translated_Review is NULL, then Sentiment must be NULL.</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT * FROM google_play_store_user_reviews WHERE "Sentiment" NOT IN ('Positive', 'Negative', 'Neutral') AND "Sentiment" IS NOT NULL;</t>
+    <t xml:space="preserve">SELECT * FROM google_play_store_user_reviews  WHERE ("Sentiment" NOT IN ('Positive', 'Negative', 'Neutral') AND "Sentiment" IS NOT NULL)  OR ("Translated_Review" IS NULL AND "Sentiment" IS NOT NULL);</t>
   </si>
   <si>
     <t xml:space="preserve">Sentiment_Polarity</t>
@@ -199,7 +205,7 @@
     <t xml:space="preserve">Value must be between -1.0 and 1.0. If Translated_Review is NULL, then Sentiment_Polarity must be NULL.</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT * FROM google_play_store_user_reviews WHERE "Sentiment_Polarity" &lt; -1 OR "Sentiment_Polarity" &gt; 1;</t>
+    <t xml:space="preserve">SELECT * FROM google_play_store_user_reviews  WHERE (("Sentiment_Polarity" &lt; -1 OR "Sentiment_Polarity" &gt; 1) AND "Sentiment_Polarity" IS NOT NULL) OR ("Translated_Review" IS NULL AND "Sentiment_Polarity" IS NOT NULL); </t>
   </si>
   <si>
     <t xml:space="preserve">If Sentiment is 'Positive', then Sentiment_Polarity must be &gt; 0 and &lt;= 1.</t>
@@ -232,7 +238,7 @@
     <t xml:space="preserve">Value must be between 0.0 and 1.0. If Translated_Review is NULL, then Sentiment_Subjectivity must be NULL.</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT * FROM google_play_store_user_reviews WHERE "Sentiment_Subjectivity" &lt; 0 OR "Sentiment_Subjectivity" &gt; 1;</t>
+    <t xml:space="preserve">SELECT * FROM google_play_store_user_reviews  WHERE (("Sentiment_Subjectivity" &lt; 0 OR "Sentiment_Subjectivity" &gt; 1) AND "Sentiment_Subjectivity" IS NOT NULL) OR ("Translated_Review" IS NULL AND "Sentiment_Subjectivity" IS NOT NULL); </t>
   </si>
 </sst>
 </file>
@@ -242,7 +248,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -278,12 +284,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -469,7 +469,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -480,6 +480,10 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,10 +505,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -655,7 +655,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="67.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="76.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="8" customFormat="true" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
@@ -694,7 +694,9 @@
       <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7"/>
+      <c r="F2" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="n">
@@ -704,16 +706,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="7" t="s">
         <v>13</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -724,16 +726,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="10" t="s">
         <v>17</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -744,16 +746,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="E5" s="12" t="s">
         <v>21</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -764,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="10" t="s">
         <v>24</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" s="8" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -784,16 +786,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="10" t="s">
         <v>27</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -804,16 +806,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="10" t="s">
         <v>30</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -824,16 +826,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="10" t="s">
         <v>34</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -844,72 +846,74 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="10" t="s">
         <v>37</v>
       </c>
+      <c r="F10" s="11" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="11" s="8" customFormat="true" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
     </row>
     <row r="12" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -917,19 +921,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -937,19 +941,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -957,19 +961,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>53</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17" s="8" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -977,19 +981,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="10" t="s">
         <v>56</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="18" s="8" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -997,19 +1001,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="10" t="s">
         <v>59</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="19" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1017,19 +1021,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1037,19 +1041,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="10" t="s">
         <v>64</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="21" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1057,19 +1061,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>67</v>
+        <v>32</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="22" s="8" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1077,19 +1081,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="10" t="s">
         <v>70</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1098,7 +1102,7 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="10"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1106,7 +1110,7 @@
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="10"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
@@ -1114,7 +1118,7 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="10"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
@@ -1122,7 +1126,7 @@
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
+      <c r="F26" s="10"/>
     </row>
     <row r="27" s="8" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
@@ -1138,7 +1142,7 @@
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="10"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" s="8" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18"/>
@@ -1153,8 +1157,8 @@
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="10"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" s="22" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20"/>
@@ -1169,8 +1173,8 @@
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="10"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20"/>
